--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,20 +895,20 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
         <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="15">
         <v>6</v>
@@ -926,7 +926,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H16" s="14">
-        <v>-30.769230769230</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K16" s="14">
-        <v>-35.294117647058</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="L16" s="14">
-        <v>-72.5</v>
+        <v>-65.116279069767</v>
       </c>
       <c r="M16" s="14">
-        <v>-64.516129032258</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.791044776119</v>
+        <v>-90.740740740740</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14">
-        <v>16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H17" s="14">
-        <v>-25</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J17" s="15">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="K17" s="14">
-        <v>-21.739130434782</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="L17" s="14">
-        <v>-18.181818181818</v>
+        <v>-10</v>
       </c>
       <c r="M17" s="14">
-        <v>176.923076923077</v>
+        <v>181.25</v>
       </c>
       <c r="N17" s="14">
-        <v>2.857142857142</v>
+        <v>15.384615384615</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" s="14">
-        <v>-14.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H18" s="14">
-        <v>-65.853658536585</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J18" s="15">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K18" s="14">
-        <v>-65.625</v>
+        <v>-64.864864864864</v>
       </c>
       <c r="L18" s="14">
-        <v>-57.692307692307</v>
+        <v>-55.932203389830</v>
       </c>
       <c r="M18" s="14">
-        <v>-59.259259259259</v>
+        <v>-61.764705882352</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.517006802721</v>
+        <v>-92.073170731707</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E19" s="14">
-        <v>200</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="F19" s="15">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" s="15">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H19" s="14">
-        <v>10.344827586206</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="J19" s="15">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="K19" s="14">
-        <v>35.616438356164</v>
+        <v>20.833333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>-36.942675159235</v>
+        <v>-34.831460674157</v>
       </c>
       <c r="M19" s="14">
-        <v>52.307692307692</v>
+        <v>73.134328358209</v>
       </c>
       <c r="N19" s="14">
-        <v>-29.285714285714</v>
+        <v>-28.834355828220</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>28.571428571428</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G20" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H20" s="14">
-        <v>-3.571428571428</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="I20" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J20" s="15">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K20" s="14">
-        <v>-11.111111111111</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-28.571428571428</v>
+        <v>-31.25</v>
       </c>
       <c r="M20" s="14">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.323210412147</v>
+        <v>-91.713747645951</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>37.931034482758</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="F21" s="17">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G21" s="17">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.285714285714</v>
+        <v>-22.043010752688</v>
       </c>
       <c r="I21" s="17">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="J21" s="17">
-        <v>248</v>
+        <v>299</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.709677419354</v>
+        <v>-15.719063545150</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.857142857142</v>
+        <v>-36.202531645569</v>
       </c>
       <c r="M21" s="18">
-        <v>9.743589743589</v>
+        <v>13.513513513513</v>
       </c>
       <c r="N21" s="18">
-        <v>-80</v>
+        <v>-79.512195121951</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
       </c>
       <c r="J22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1223,32 +1223,32 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>21</v>
+      <c r="J23" s="15">
+        <v>1</v>
+      </c>
+      <c r="K23" s="14">
+        <v>200</v>
       </c>
       <c r="L23" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M23" s="14">
         <v>200</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D24" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.272727272727</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="F24" s="15">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G24" s="15">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.597701149425</v>
+        <v>-10.326086956521</v>
       </c>
       <c r="I24" s="15">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="J24" s="15">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="K24" s="14">
-        <v>-1.992031872509</v>
+        <v>-3.367003367003</v>
       </c>
       <c r="L24" s="14">
-        <v>-26.347305389221</v>
+        <v>-24.671916010498</v>
       </c>
       <c r="M24" s="14">
-        <v>42.196531791907</v>
+        <v>49.479166666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D25" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E25" s="14">
-        <v>-8</v>
+        <v>3.448275862068</v>
       </c>
       <c r="F25" s="15">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G25" s="15">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H25" s="14">
-        <v>-11.650485436893</v>
+        <v>-0.952380952380</v>
       </c>
       <c r="I25" s="15">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="J25" s="15">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="K25" s="14">
-        <v>-13.605442176870</v>
+        <v>-10.795454545454</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.810426540284</v>
+        <v>-34.309623430962</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D26" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>91.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G26" s="15">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H26" s="14">
-        <v>-23.809523809523</v>
+        <v>5.357142857142</v>
       </c>
       <c r="I26" s="15">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="J26" s="15">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K26" s="14">
-        <v>-17.045454545454</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="14">
-        <v>5.797101449275</v>
+        <v>18.518518518518</v>
       </c>
       <c r="M26" s="14">
-        <v>21.666666666666</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,22 +1394,22 @@
         <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
         <v>300</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
       <c r="E28" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
         <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H28" s="14">
-        <v>-53.846153846153</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-56.25</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L28" s="14">
-        <v>-46.153846153846</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="15">
+        <v>1</v>
+      </c>
+      <c r="K29" s="14">
+        <v>-100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="15">
+        <v>1</v>
+      </c>
+      <c r="K30" s="14">
+        <v>-100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="15">
         <v>4</v>
       </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
       <c r="H15" s="14">
+        <v>-25</v>
+      </c>
+      <c r="I15" s="15">
+        <v>8</v>
+      </c>
+      <c r="J15" s="15">
+        <v>5</v>
+      </c>
+      <c r="K15" s="14">
+        <v>60</v>
+      </c>
+      <c r="L15" s="14">
+        <v>700</v>
+      </c>
+      <c r="M15" s="14">
+        <v>166.666666666667</v>
+      </c>
+      <c r="N15" s="14">
         <v>33.333333333333</v>
-      </c>
-      <c r="I15" s="15">
-        <v>6</v>
-      </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
-      <c r="K15" s="14">
-        <v>100</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="14">
-        <v>100</v>
-      </c>
-      <c r="N15" s="14">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" s="14">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-52.941176470588</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J16" s="15">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K16" s="14">
-        <v>-31.818181818181</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="L16" s="14">
-        <v>-65.116279069767</v>
+        <v>-63.461538461538</v>
       </c>
       <c r="M16" s="14">
-        <v>-57.142857142857</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.740740740740</v>
+        <v>-89.673913043478</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>7</v>
+      </c>
+      <c r="D17" s="15">
         <v>8</v>
       </c>
-      <c r="D17" s="15">
-        <v>10</v>
-      </c>
       <c r="E17" s="14">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
       <c r="F17" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G17" s="15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17" s="14">
-        <v>-22.857142857142</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I17" s="15">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J17" s="15">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K17" s="14">
-        <v>-19.642857142857</v>
+        <v>-18.75</v>
       </c>
       <c r="L17" s="14">
-        <v>-10</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M17" s="14">
-        <v>181.25</v>
+        <v>188.888888888889</v>
       </c>
       <c r="N17" s="14">
-        <v>15.384615384615</v>
+        <v>20.930232558139</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14">
-        <v>-60</v>
+        <v>25</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G18" s="15">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H18" s="14">
-        <v>-64.285714285714</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="I18" s="15">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J18" s="15">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K18" s="14">
-        <v>-64.864864864864</v>
+        <v>-56.097560975609</v>
       </c>
       <c r="L18" s="14">
-        <v>-55.932203389830</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M18" s="14">
-        <v>-61.764705882352</v>
+        <v>-52</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.073170731707</v>
+        <v>-90.374331550802</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D19" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E19" s="14">
-        <v>-30.434782608695</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F19" s="15">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G19" s="15">
         <v>60</v>
       </c>
       <c r="H19" s="14">
-        <v>8.333333333333</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="J19" s="15">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="K19" s="14">
-        <v>20.833333333333</v>
+        <v>19.130434782608</v>
       </c>
       <c r="L19" s="14">
-        <v>-34.831460674157</v>
+        <v>-32.178217821782</v>
       </c>
       <c r="M19" s="14">
-        <v>73.134328358209</v>
+        <v>75.641025641025</v>
       </c>
       <c r="N19" s="14">
-        <v>-28.834355828220</v>
+        <v>-25.543478260869</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E20" s="14">
-        <v>33.333333333333</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F20" s="15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G20" s="15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H20" s="14">
-        <v>-10.344827586206</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="J20" s="15">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K20" s="14">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-31.25</v>
+        <v>-11.594202898550</v>
       </c>
       <c r="M20" s="14">
-        <v>37.5</v>
+        <v>74.285714285714</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.713747645951</v>
+        <v>-89.900662251655</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D21" s="17">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.450980392156</v>
+        <v>7.017543859649</v>
       </c>
       <c r="F21" s="17">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="G21" s="17">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.043010752688</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="I21" s="17">
-        <v>252</v>
+        <v>313</v>
       </c>
       <c r="J21" s="17">
-        <v>299</v>
+        <v>356</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.719063545150</v>
+        <v>-12.078651685393</v>
       </c>
       <c r="L21" s="18">
-        <v>-36.202531645569</v>
+        <v>-30.133928571428</v>
       </c>
       <c r="M21" s="18">
-        <v>13.513513513513</v>
+        <v>25.702811244979</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.512195121951</v>
+        <v>-77.578796561604</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
         <v>-100</v>
@@ -1192,19 +1192,19 @@
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
       </c>
       <c r="J22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L22" s="14">
         <v>-33.333333333333</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14">
         <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M23" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D24" s="15">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E24" s="14">
-        <v>-13.043478260869</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="F24" s="15">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="G24" s="15">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="H24" s="14">
-        <v>-10.326086956521</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="I24" s="15">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="J24" s="15">
-        <v>297</v>
+        <v>350</v>
       </c>
       <c r="K24" s="14">
-        <v>-3.367003367003</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.671916010498</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="M24" s="14">
-        <v>49.479166666666</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D25" s="15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E25" s="14">
-        <v>3.448275862068</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F25" s="15">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G25" s="15">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="H25" s="14">
-        <v>-0.952380952380</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="I25" s="15">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="J25" s="15">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="K25" s="14">
-        <v>-10.795454545454</v>
+        <v>-13.397129186602</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.309623430962</v>
+        <v>-34.420289855072</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E26" s="14">
-        <v>91.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F26" s="15">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G26" s="15">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H26" s="14">
-        <v>5.357142857142</v>
+        <v>5</v>
       </c>
       <c r="I26" s="15">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="J26" s="15">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="K26" s="14">
-        <v>-4</v>
+        <v>-8.264462809917</v>
       </c>
       <c r="L26" s="14">
-        <v>18.518518518518</v>
+        <v>6.730769230769</v>
       </c>
       <c r="M26" s="14">
-        <v>41.176470588235</v>
+        <v>35.365853658536</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="14">
         <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>300</v>
+        <v>233.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>100</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>11</v>
       </c>
       <c r="H28" s="14">
-        <v>-45.454545454545</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
         <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-47.058823529411</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L28" s="14">
-        <v>-35.714285714285</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,35 +892,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="15">
         <v>2</v>
       </c>
       <c r="E15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>60</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L15" s="14">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="M15" s="14">
         <v>166.666666666667</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>7</v>
       </c>
       <c r="E16" s="14">
-        <v>-42.857142857142</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F16" s="15">
         <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" s="14">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I16" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" s="15">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K16" s="14">
-        <v>-34.482758620689</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-63.461538461538</v>
+        <v>-64.406779661017</v>
       </c>
       <c r="M16" s="14">
-        <v>-51.282051282051</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.673913043478</v>
+        <v>-89.603960396039</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="14">
-        <v>-12.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F17" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" s="15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H17" s="14">
-        <v>-11.764705882352</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="I17" s="15">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J17" s="15">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="K17" s="14">
-        <v>-18.75</v>
+        <v>-18.666666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>-8.771929824561</v>
+        <v>-7.575757575757</v>
       </c>
       <c r="M17" s="14">
-        <v>188.888888888889</v>
+        <v>205</v>
       </c>
       <c r="N17" s="14">
-        <v>20.930232558139</v>
+        <v>32.608695652173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D18" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G18" s="15">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H18" s="14">
-        <v>-40.540540540540</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="I18" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J18" s="15">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K18" s="14">
-        <v>-56.097560975609</v>
+        <v>-52.272727272727</v>
       </c>
       <c r="L18" s="14">
-        <v>-45.454545454545</v>
+        <v>-42.465753424657</v>
       </c>
       <c r="M18" s="14">
-        <v>-52</v>
+        <v>-49.397590361445</v>
       </c>
       <c r="N18" s="14">
-        <v>-90.374331550802</v>
+        <v>-89.781021897810</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19" s="14">
-        <v>10.526315789473</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G19" s="15">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="H19" s="14">
-        <v>13.333333333333</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="I19" s="15">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="J19" s="15">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="K19" s="14">
-        <v>19.130434782608</v>
+        <v>6.474820143884</v>
       </c>
       <c r="L19" s="14">
-        <v>-32.178217821782</v>
+        <v>-37.288135593220</v>
       </c>
       <c r="M19" s="14">
-        <v>75.641025641025</v>
+        <v>68.181818181818</v>
       </c>
       <c r="N19" s="14">
-        <v>-25.543478260869</v>
+        <v>-28.502415458937</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
         <v>13</v>
       </c>
       <c r="E20" s="14">
-        <v>30.769230769230</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F20" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G20" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="I20" s="15">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J20" s="15">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="L20" s="14">
-        <v>-11.594202898550</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="M20" s="14">
-        <v>74.285714285714</v>
+        <v>37.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.900662251655</v>
+        <v>-90.178571428571</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E21" s="18">
-        <v>7.017543859649</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F21" s="17">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G21" s="17">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.638297872340</v>
+        <v>-15</v>
       </c>
       <c r="I21" s="17">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="J21" s="17">
-        <v>356</v>
+        <v>419</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.078651685393</v>
+        <v>-17.422434367541</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.133928571428</v>
+        <v>-32.553606237816</v>
       </c>
       <c r="M21" s="18">
-        <v>25.702811244979</v>
+        <v>21.403508771929</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.578796561604</v>
+        <v>-77.605177993527</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
         <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J23" s="15">
         <v>2</v>
       </c>
       <c r="K23" s="14">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L23" s="14">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M23" s="14">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D24" s="15">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E24" s="14">
-        <v>-37.735849056603</v>
+        <v>-26</v>
       </c>
       <c r="F24" s="15">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G24" s="15">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H24" s="14">
-        <v>-25.373134328358</v>
+        <v>-26.943005181347</v>
       </c>
       <c r="I24" s="15">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="J24" s="15">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="K24" s="14">
-        <v>-8.571428571428</v>
+        <v>-11</v>
       </c>
       <c r="L24" s="14">
-        <v>-25.925925925925</v>
+        <v>-28.657314629258</v>
       </c>
       <c r="M24" s="14">
-        <v>45.454545454545</v>
+        <v>47.717842323651</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E25" s="14">
-        <v>-27.272727272727</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="F25" s="15">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G25" s="15">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H25" s="14">
-        <v>-13.114754098360</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I25" s="15">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="J25" s="15">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="K25" s="14">
-        <v>-13.397129186602</v>
+        <v>-16.460905349794</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.420289855072</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E26" s="14">
-        <v>-28.571428571428</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F26" s="15">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G26" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H26" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J26" s="15">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="K26" s="14">
-        <v>-8.264462809917</v>
+        <v>-10.791366906474</v>
       </c>
       <c r="L26" s="14">
-        <v>6.730769230769</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>35.365853658536</v>
+        <v>34.782608695652</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="15">
         <v>2</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>66.666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="L27" s="14">
-        <v>233.333333333333</v>
+        <v>175</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>100</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-63.636363636363</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="14">
-        <v>-52.941176470588</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L28" s="14">
-        <v>-50</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L15" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M15" s="14">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
         <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="14">
-        <v>-45.454545454545</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K16" s="14">
-        <v>-41.666666666666</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="L16" s="14">
-        <v>-64.406779661017</v>
+        <v>-63.492063492063</v>
       </c>
       <c r="M16" s="14">
         <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.603960396039</v>
+        <v>-89.047619047619</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="15">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-27.272727272727</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G17" s="15">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H17" s="14">
-        <v>-11.428571428571</v>
+        <v>3.125</v>
       </c>
       <c r="I17" s="15">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J17" s="15">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K17" s="14">
-        <v>-18.666666666666</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="L17" s="14">
-        <v>-7.575757575757</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M17" s="14">
-        <v>205</v>
+        <v>204.347826086957</v>
       </c>
       <c r="N17" s="14">
-        <v>32.608695652173</v>
+        <v>32.075471698113</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E18" s="14">
-        <v>16.666666666666</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F18" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G18" s="15">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H18" s="14">
-        <v>-16.129032258064</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="15">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J18" s="15">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="K18" s="14">
-        <v>-52.272727272727</v>
+        <v>-49.019607843137</v>
       </c>
       <c r="L18" s="14">
-        <v>-42.465753424657</v>
+        <v>-35</v>
       </c>
       <c r="M18" s="14">
-        <v>-49.397590361445</v>
+        <v>-41.573033707865</v>
       </c>
       <c r="N18" s="14">
-        <v>-89.781021897810</v>
+        <v>-88.596491228070</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E19" s="14">
-        <v>-54.166666666666</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F19" s="15">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G19" s="15">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H19" s="14">
-        <v>-11.267605633802</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I19" s="15">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J19" s="15">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="K19" s="14">
-        <v>6.474820143884</v>
+        <v>1.265822784810</v>
       </c>
       <c r="L19" s="14">
-        <v>-37.288135593220</v>
+        <v>-37.743190661478</v>
       </c>
       <c r="M19" s="14">
-        <v>68.181818181818</v>
+        <v>58.415841584158</v>
       </c>
       <c r="N19" s="14">
-        <v>-28.502415458937</v>
+        <v>-28.888888888888</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20" s="15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E20" s="14">
-        <v>-61.538461538461</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F20" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G20" s="15">
         <v>36</v>
       </c>
       <c r="H20" s="14">
-        <v>-2.777777777777</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I20" s="15">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="J20" s="15">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K20" s="14">
-        <v>-10.810810810810</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L20" s="14">
-        <v>-13.157894736842</v>
+        <v>-8.235294117647</v>
       </c>
       <c r="M20" s="14">
-        <v>37.5</v>
+        <v>44.444444444444</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.178571428571</v>
+        <v>-89.709762532981</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>-47.619047619047</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G21" s="17">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="H21" s="18">
-        <v>-15</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="I21" s="17">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="J21" s="17">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.422434367541</v>
+        <v>-15.517241379310</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.553606237816</v>
+        <v>-30.373001776198</v>
       </c>
       <c r="M21" s="18">
-        <v>21.403508771929</v>
+        <v>23.659305993690</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.605177993527</v>
+        <v>-77.062609713282</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
@@ -1207,7 +1207,7 @@
         <v>-60</v>
       </c>
       <c r="L22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>3</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1251,7 +1251,7 @@
         <v>75</v>
       </c>
       <c r="M23" s="14">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D24" s="15">
         <v>50</v>
       </c>
       <c r="E24" s="14">
-        <v>-26</v>
+        <v>-46</v>
       </c>
       <c r="F24" s="15">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G24" s="15">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H24" s="14">
-        <v>-26.943005181347</v>
+        <v>-31.658291457286</v>
       </c>
       <c r="I24" s="15">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="J24" s="15">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K24" s="14">
-        <v>-11</v>
+        <v>-15.333333333333</v>
       </c>
       <c r="L24" s="14">
-        <v>-28.657314629258</v>
+        <v>-31.103074141048</v>
       </c>
       <c r="M24" s="14">
-        <v>47.717842323651</v>
+        <v>36.559139784946</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E25" s="14">
-        <v>-32.352941176470</v>
+        <v>-69.767441860465</v>
       </c>
       <c r="F25" s="15">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G25" s="15">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H25" s="14">
-        <v>-18.181818181818</v>
+        <v>-35.971223021582</v>
       </c>
       <c r="I25" s="15">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J25" s="15">
-        <v>243</v>
+        <v>286</v>
       </c>
       <c r="K25" s="14">
-        <v>-16.460905349794</v>
+        <v>-24.475524475524</v>
       </c>
       <c r="L25" s="14">
-        <v>-36.363636363636</v>
+        <v>-38.983050847457</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E26" s="14">
-        <v>-38.888888888888</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F26" s="15">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G26" s="15">
         <v>65</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>4.615384615384</v>
       </c>
       <c r="I26" s="15">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="J26" s="15">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K26" s="14">
-        <v>-10.791366906474</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="L26" s="14">
-        <v>3.333333333333</v>
+        <v>5.223880597014</v>
       </c>
       <c r="M26" s="14">
-        <v>34.782608695652</v>
+        <v>31.775700934579</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-50</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="15">
         <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="L27" s="14">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>3</v>
+      </c>
+      <c r="G28" s="15">
         <v>2</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>4</v>
-      </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>-44.444444444444</v>
       </c>
       <c r="L28" s="14">
-        <v>-47.368421052631</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -911,22 +911,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="14">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-42.857142857142</v>
+        <v>-35</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K16" s="14">
-        <v>-39.473684210526</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-63.492063492063</v>
+        <v>-61.643835616438</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-45.098039215686</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.047619047619</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>200</v>
+        <v>62.5</v>
       </c>
       <c r="F17" s="15">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G17" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H17" s="14">
-        <v>3.125</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="J17" s="15">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K17" s="14">
-        <v>-10.256410256410</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="L17" s="14">
-        <v>-6.666666666666</v>
+        <v>2.439024390243</v>
       </c>
       <c r="M17" s="14">
-        <v>204.347826086957</v>
+        <v>189.655172413793</v>
       </c>
       <c r="N17" s="14">
-        <v>32.075471698113</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-35.714285714285</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="15">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H18" s="14">
-        <v>-21.052631578947</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="I18" s="15">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J18" s="15">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K18" s="14">
-        <v>-49.019607843137</v>
+        <v>-47.663551401869</v>
       </c>
       <c r="L18" s="14">
-        <v>-35</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M18" s="14">
-        <v>-41.573033707865</v>
+        <v>-43.434343434343</v>
       </c>
       <c r="N18" s="14">
-        <v>-88.596491228070</v>
+        <v>-88.844621513944</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E19" s="14">
-        <v>-36.842105263157</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F19" s="15">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G19" s="15">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H19" s="14">
-        <v>-29.411764705882</v>
+        <v>-37.349397590361</v>
       </c>
       <c r="I19" s="15">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J19" s="15">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="K19" s="14">
-        <v>1.265822784810</v>
+        <v>-5.586592178770</v>
       </c>
       <c r="L19" s="14">
-        <v>-37.743190661478</v>
+        <v>-38.989169675090</v>
       </c>
       <c r="M19" s="14">
-        <v>58.415841584158</v>
+        <v>52.252252252252</v>
       </c>
       <c r="N19" s="14">
-        <v>-28.888888888888</v>
+        <v>-29.875518672199</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="14">
-        <v>71.428571428571</v>
+        <v>137.5</v>
       </c>
       <c r="F20" s="15">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G20" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H20" s="14">
-        <v>5.555555555555</v>
+        <v>29.268292682926</v>
       </c>
       <c r="I20" s="15">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="J20" s="15">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K20" s="14">
-        <v>-3.703703703703</v>
+        <v>10.112359550561</v>
       </c>
       <c r="L20" s="14">
-        <v>-8.235294117647</v>
+        <v>4.255319148936</v>
       </c>
       <c r="M20" s="14">
-        <v>44.444444444444</v>
+        <v>53.125</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.709762532981</v>
+        <v>-87.916152897657</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>13.043478260869</v>
       </c>
       <c r="F21" s="17">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="G21" s="17">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.055555555555</v>
+        <v>-10.426540284360</v>
       </c>
       <c r="I21" s="17">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="J21" s="17">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.517241379310</v>
+        <v>-12.745098039215</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.373001776198</v>
+        <v>-27.876823338735</v>
       </c>
       <c r="M21" s="18">
-        <v>23.659305993690</v>
+        <v>24.301675977653</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.062609713282</v>
+        <v>-75.880758807588</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1201,13 +1201,13 @@
         <v>2</v>
       </c>
       <c r="J22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="L22" s="14">
         <v>-60</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-50</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>100</v>
       </c>
       <c r="F23" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15">
         <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I23" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="L23" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M23" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D24" s="15">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E24" s="14">
-        <v>-46</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="F24" s="15">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G24" s="15">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="H24" s="14">
-        <v>-31.658291457286</v>
+        <v>-32.093023255814</v>
       </c>
       <c r="I24" s="15">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="J24" s="15">
-        <v>450</v>
+        <v>512</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.333333333333</v>
+        <v>-15.8203125</v>
       </c>
       <c r="L24" s="14">
-        <v>-31.103074141048</v>
+        <v>-27.563025210084</v>
       </c>
       <c r="M24" s="14">
-        <v>36.559139784946</v>
+        <v>45.117845117845</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E25" s="14">
-        <v>-69.767441860465</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G25" s="15">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H25" s="14">
-        <v>-35.971223021582</v>
+        <v>-47.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="J25" s="15">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="K25" s="14">
-        <v>-24.475524475524</v>
+        <v>-27.607361963190</v>
       </c>
       <c r="L25" s="14">
-        <v>-38.983050847457</v>
+        <v>-37.234042553191</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D26" s="15">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E26" s="14">
-        <v>21.428571428571</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="15">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G26" s="15">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H26" s="14">
-        <v>4.615384615384</v>
+        <v>-13.698630136986</v>
       </c>
       <c r="I26" s="15">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J26" s="15">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="K26" s="14">
-        <v>-7.843137254901</v>
+        <v>-8.670520231213</v>
       </c>
       <c r="L26" s="14">
-        <v>5.223880597014</v>
+        <v>2.597402597402</v>
       </c>
       <c r="M26" s="14">
-        <v>31.775700934579</v>
+        <v>31.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>5</v>
       </c>
       <c r="G27" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I27" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="15">
         <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="L27" s="14">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="14">
-        <v>-44.444444444444</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="L28" s="14">
-        <v>-54.545454545454</v>
+        <v>-60</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>-100</v>
       </c>
       <c r="I33" s="15">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14">
+        <v>0</v>
       </c>
       <c r="L33" s="14">
         <v>-85.714285714285</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
         <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="L15" s="14">
-        <v>400</v>
+        <v>175</v>
       </c>
       <c r="M15" s="14">
-        <v>233.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N15" s="14">
-        <v>66.666666666666</v>
+        <v>57.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-35</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J16" s="15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K16" s="14">
-        <v>-33.333333333333</v>
+        <v>-31.111111111111</v>
       </c>
       <c r="L16" s="14">
-        <v>-61.643835616438</v>
+        <v>-59.740259740259</v>
       </c>
       <c r="M16" s="14">
-        <v>-45.098039215686</v>
+        <v>-42.592592592592</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.5</v>
+        <v>-87.795275590551</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H17" s="14">
-        <v>26.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I17" s="15">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J17" s="15">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K17" s="14">
-        <v>-2.325581395348</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>2.439024390243</v>
+        <v>5.747126436781</v>
       </c>
       <c r="M17" s="14">
-        <v>189.655172413793</v>
+        <v>178.787878787879</v>
       </c>
       <c r="N17" s="14">
-        <v>40</v>
+        <v>41.538461538461</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G18" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H18" s="14">
-        <v>-12.121212121212</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="I18" s="15">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J18" s="15">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K18" s="14">
-        <v>-47.663551401869</v>
+        <v>-47.899159663865</v>
       </c>
       <c r="L18" s="14">
-        <v>-36.363636363636</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-43.434343434343</v>
+        <v>-42.592592592592</v>
       </c>
       <c r="N18" s="14">
-        <v>-88.844621513944</v>
+        <v>-88.706739526411</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D19" s="15">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-57.142857142857</v>
+        <v>118.181818181818</v>
       </c>
       <c r="F19" s="15">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G19" s="15">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H19" s="14">
-        <v>-37.349397590361</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I19" s="15">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="J19" s="15">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.586592178770</v>
+        <v>1.578947368421</v>
       </c>
       <c r="L19" s="14">
-        <v>-38.989169675090</v>
+        <v>-36.928104575163</v>
       </c>
       <c r="M19" s="14">
-        <v>52.252252252252</v>
+        <v>58.196721311475</v>
       </c>
       <c r="N19" s="14">
-        <v>-29.875518672199</v>
+        <v>-26.053639846743</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>137.5</v>
+        <v>500</v>
       </c>
       <c r="F20" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="15">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H20" s="14">
-        <v>29.268292682926</v>
+        <v>74.193548387096</v>
       </c>
       <c r="I20" s="15">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="J20" s="15">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K20" s="14">
-        <v>10.112359550561</v>
+        <v>26.086956521739</v>
       </c>
       <c r="L20" s="14">
-        <v>4.255319148936</v>
+        <v>9.433962264150</v>
       </c>
       <c r="M20" s="14">
-        <v>53.125</v>
+        <v>70.588235294117</v>
       </c>
       <c r="N20" s="14">
-        <v>-87.916152897657</v>
+        <v>-86.773090079817</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D21" s="17">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>13.043478260869</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G21" s="17">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.426540284360</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="I21" s="17">
-        <v>445</v>
+        <v>505</v>
       </c>
       <c r="J21" s="17">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.745098039215</v>
+        <v>-7.509157509157</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.876823338735</v>
+        <v>-25.406203840472</v>
       </c>
       <c r="M21" s="18">
-        <v>24.301675977653</v>
+        <v>29.820051413881</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.880758807588</v>
+        <v>-74.925521350546</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="15">
         <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="15">
-        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1207,7 +1207,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="15">
         <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I23" s="15">
         <v>9</v>
       </c>
       <c r="J23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="14">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="L23" s="14">
         <v>80</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D24" s="15">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E24" s="14">
-        <v>-19.354838709677</v>
+        <v>20.370370370370</v>
       </c>
       <c r="F24" s="15">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="G24" s="15">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H24" s="14">
-        <v>-32.093023255814</v>
+        <v>-17.129629629629</v>
       </c>
       <c r="I24" s="15">
-        <v>431</v>
+        <v>496</v>
       </c>
       <c r="J24" s="15">
-        <v>512</v>
+        <v>566</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.8203125</v>
+        <v>-12.367491166077</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.563025210084</v>
+        <v>-22.620904836193</v>
       </c>
       <c r="M24" s="14">
-        <v>45.117845117845</v>
+        <v>55.974842767295</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D25" s="15">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>14.705882352941</v>
       </c>
       <c r="F25" s="15">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="G25" s="15">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H25" s="14">
-        <v>-47.333333333333</v>
+        <v>-37.086092715231</v>
       </c>
       <c r="I25" s="15">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="J25" s="15">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="K25" s="14">
-        <v>-27.607361963190</v>
+        <v>-23.611111111111</v>
       </c>
       <c r="L25" s="14">
-        <v>-37.234042553191</v>
+        <v>-31.761786600496</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D26" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E26" s="14">
-        <v>-10</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="F26" s="15">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G26" s="15">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H26" s="14">
-        <v>-13.698630136986</v>
+        <v>-10.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="J26" s="15">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="K26" s="14">
-        <v>-8.670520231213</v>
+        <v>-9.693877551020</v>
       </c>
       <c r="L26" s="14">
-        <v>2.597402597402</v>
+        <v>3.508771929824</v>
       </c>
       <c r="M26" s="14">
-        <v>31.666666666666</v>
+        <v>36.153846153846</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>62.5</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L27" s="14">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>3</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K28" s="14">
-        <v>-47.368421052631</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L28" s="14">
-        <v>-60</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>4</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>4</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,260 +878,260 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="M14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>300</v>
+      </c>
+      <c r="M14" s="15">
+        <v>300</v>
+      </c>
+      <c r="N14" s="15">
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
-        <v>11</v>
-      </c>
-      <c r="J15" s="15">
-        <v>8</v>
-      </c>
-      <c r="K15" s="14">
-        <v>37.5</v>
-      </c>
-      <c r="L15" s="14">
-        <v>175</v>
-      </c>
-      <c r="M15" s="14">
-        <v>266.666666666667</v>
-      </c>
-      <c r="N15" s="14">
-        <v>57.142857142857</v>
+      <c r="E15" s="15">
+        <v>200</v>
+      </c>
+      <c r="F15" s="14">
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>200</v>
+      </c>
+      <c r="I15" s="14">
+        <v>14</v>
+      </c>
+      <c r="J15" s="14">
+        <v>9</v>
+      </c>
+      <c r="K15" s="15">
+        <v>55.555555555555</v>
+      </c>
+      <c r="L15" s="15">
+        <v>250</v>
+      </c>
+      <c r="M15" s="15">
+        <v>366.666666666667</v>
+      </c>
+      <c r="N15" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>3</v>
-      </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
-        <v>12</v>
-      </c>
-      <c r="G16" s="15">
-        <v>16</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-25</v>
-      </c>
-      <c r="I16" s="15">
-        <v>31</v>
-      </c>
-      <c r="J16" s="15">
-        <v>45</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-31.111111111111</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-59.740259740259</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-42.592592592592</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-87.795275590551</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>6</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="F16" s="14">
+        <v>11</v>
+      </c>
+      <c r="G16" s="14">
+        <v>15</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-26.666666666666</v>
+      </c>
+      <c r="I16" s="14">
+        <v>32</v>
+      </c>
+      <c r="J16" s="14">
+        <v>51</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-37.254901960784</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-62.352941176470</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-41.818181818181</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-88.321167883211</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>6</v>
-      </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
-      <c r="E17" s="14">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
-        <v>36</v>
-      </c>
-      <c r="G17" s="15">
-        <v>28</v>
-      </c>
-      <c r="H17" s="14">
-        <v>28.571428571428</v>
-      </c>
-      <c r="I17" s="15">
-        <v>92</v>
-      </c>
-      <c r="J17" s="15">
-        <v>92</v>
-      </c>
-      <c r="K17" s="14">
-        <v>0</v>
-      </c>
-      <c r="L17" s="14">
-        <v>5.747126436781</v>
-      </c>
-      <c r="M17" s="14">
-        <v>178.787878787879</v>
-      </c>
-      <c r="N17" s="14">
-        <v>41.538461538461</v>
+      <c r="C17" s="14">
+        <v>14</v>
+      </c>
+      <c r="D17" s="14">
+        <v>8</v>
+      </c>
+      <c r="E17" s="15">
+        <v>75</v>
+      </c>
+      <c r="F17" s="14">
+        <v>41</v>
+      </c>
+      <c r="G17" s="14">
+        <v>25</v>
+      </c>
+      <c r="H17" s="15">
+        <v>64</v>
+      </c>
+      <c r="I17" s="14">
+        <v>105</v>
+      </c>
+      <c r="J17" s="14">
+        <v>100</v>
+      </c>
+      <c r="K17" s="15">
+        <v>5</v>
+      </c>
+      <c r="L17" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="M17" s="15">
+        <v>176.315789473684</v>
+      </c>
+      <c r="N17" s="15">
+        <v>45.833333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>5</v>
-      </c>
-      <c r="D18" s="15">
-        <v>12</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-58.333333333333</v>
-      </c>
-      <c r="F18" s="15">
-        <v>25</v>
-      </c>
-      <c r="G18" s="15">
-        <v>37</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-32.432432432432</v>
-      </c>
-      <c r="I18" s="15">
-        <v>62</v>
-      </c>
-      <c r="J18" s="15">
-        <v>119</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-47.899159663865</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-35.416666666666</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-42.592592592592</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-88.706739526411</v>
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
+        <v>8</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>22</v>
+      </c>
+      <c r="G18" s="14">
+        <v>39</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-43.589743589743</v>
+      </c>
+      <c r="I18" s="14">
+        <v>66</v>
+      </c>
+      <c r="J18" s="14">
+        <v>127</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-48.031496062992</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-35.922330097087</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-40</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-88.926174496644</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>24</v>
-      </c>
-      <c r="D19" s="15">
-        <v>11</v>
-      </c>
-      <c r="E19" s="14">
-        <v>118.181818181818</v>
-      </c>
-      <c r="F19" s="15">
-        <v>55</v>
-      </c>
-      <c r="G19" s="15">
-        <v>75</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-26.666666666666</v>
-      </c>
-      <c r="I19" s="15">
-        <v>193</v>
-      </c>
-      <c r="J19" s="15">
-        <v>190</v>
-      </c>
-      <c r="K19" s="14">
-        <v>1.578947368421</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-36.928104575163</v>
-      </c>
-      <c r="M19" s="14">
-        <v>58.196721311475</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-26.053639846743</v>
+      <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="14">
+        <v>26</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-38.461538461538</v>
+      </c>
+      <c r="F19" s="14">
+        <v>61</v>
+      </c>
+      <c r="G19" s="14">
+        <v>77</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-20.779220779220</v>
+      </c>
+      <c r="I19" s="14">
+        <v>209</v>
+      </c>
+      <c r="J19" s="14">
+        <v>216</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-3.240740740740</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-36.666666666666</v>
+      </c>
+      <c r="M19" s="15">
+        <v>57.142857142857</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-25.886524822695</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>18</v>
-      </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>500</v>
-      </c>
-      <c r="F20" s="15">
-        <v>54</v>
-      </c>
-      <c r="G20" s="15">
-        <v>31</v>
-      </c>
-      <c r="H20" s="14">
-        <v>74.193548387096</v>
-      </c>
-      <c r="I20" s="15">
-        <v>116</v>
-      </c>
-      <c r="J20" s="15">
-        <v>92</v>
-      </c>
-      <c r="K20" s="14">
-        <v>26.086956521739</v>
-      </c>
-      <c r="L20" s="14">
-        <v>9.433962264150</v>
-      </c>
-      <c r="M20" s="14">
-        <v>70.588235294117</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-86.773090079817</v>
+      <c r="C20" s="14">
+        <v>10</v>
+      </c>
+      <c r="D20" s="14">
+        <v>10</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>59</v>
+      </c>
+      <c r="G20" s="14">
+        <v>28</v>
+      </c>
+      <c r="H20" s="15">
+        <v>110.714285714286</v>
+      </c>
+      <c r="I20" s="14">
+        <v>126</v>
+      </c>
+      <c r="J20" s="14">
+        <v>102</v>
+      </c>
+      <c r="K20" s="15">
+        <v>23.529411764705</v>
+      </c>
+      <c r="L20" s="15">
+        <v>11.504424778761</v>
+      </c>
+      <c r="M20" s="15">
+        <v>72.602739726027</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-86.915887850467</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E21" s="18">
-        <v>58.333333333333</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="F21" s="17">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="G21" s="17">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.631578947368</v>
+        <v>9.677419354838</v>
       </c>
       <c r="I21" s="17">
-        <v>505</v>
+        <v>556</v>
       </c>
       <c r="J21" s="17">
-        <v>546</v>
+        <v>605</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.509157509157</v>
+        <v>-8.099173553719</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.406203840472</v>
+        <v>-23.415977961432</v>
       </c>
       <c r="M21" s="18">
-        <v>29.820051413881</v>
+        <v>34.624697336561</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.925521350546</v>
+        <v>-74.669703872437</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,31 +1182,31 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
         <v>-100</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="J22" s="15">
-        <v>6</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="L22" s="14">
+      <c r="J22" s="14">
+        <v>7</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-71.428571428571</v>
+      </c>
+      <c r="L22" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="M22" s="13" t="s">
@@ -1223,34 +1223,34 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="15">
         <v>-100</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="14">
+        <v>2</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I23" s="14">
+        <v>9</v>
+      </c>
+      <c r="J23" s="14">
         <v>5</v>
       </c>
-      <c r="G23" s="15">
-        <v>2</v>
-      </c>
-      <c r="H23" s="14">
-        <v>150</v>
-      </c>
-      <c r="I23" s="15">
-        <v>9</v>
-      </c>
-      <c r="J23" s="15">
-        <v>4</v>
-      </c>
-      <c r="K23" s="14">
-        <v>125</v>
-      </c>
-      <c r="L23" s="14">
+      <c r="K23" s="15">
         <v>80</v>
       </c>
-      <c r="M23" s="14">
+      <c r="L23" s="15">
+        <v>50</v>
+      </c>
+      <c r="M23" s="15">
         <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>65</v>
-      </c>
-      <c r="D24" s="15">
-        <v>54</v>
-      </c>
-      <c r="E24" s="14">
-        <v>20.370370370370</v>
-      </c>
-      <c r="F24" s="15">
-        <v>179</v>
-      </c>
-      <c r="G24" s="15">
-        <v>216</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-17.129629629629</v>
-      </c>
-      <c r="I24" s="15">
-        <v>496</v>
-      </c>
-      <c r="J24" s="15">
-        <v>566</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-12.367491166077</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-22.620904836193</v>
-      </c>
-      <c r="M24" s="14">
-        <v>55.974842767295</v>
+      <c r="C24" s="14">
+        <v>48</v>
+      </c>
+      <c r="D24" s="14">
+        <v>68</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-29.411764705882</v>
+      </c>
+      <c r="F24" s="14">
+        <v>190</v>
+      </c>
+      <c r="G24" s="14">
+        <v>234</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-18.803418803418</v>
+      </c>
+      <c r="I24" s="14">
+        <v>544</v>
+      </c>
+      <c r="J24" s="14">
+        <v>634</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-14.195583596214</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-22.617354196301</v>
+      </c>
+      <c r="M24" s="15">
+        <v>57.681159420289</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>39</v>
-      </c>
-      <c r="D25" s="15">
-        <v>34</v>
-      </c>
-      <c r="E25" s="14">
-        <v>14.705882352941</v>
-      </c>
-      <c r="F25" s="15">
-        <v>95</v>
-      </c>
-      <c r="G25" s="15">
-        <v>151</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-37.086092715231</v>
-      </c>
-      <c r="I25" s="15">
-        <v>275</v>
-      </c>
-      <c r="J25" s="15">
-        <v>360</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-23.611111111111</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-31.761786600496</v>
+      <c r="C25" s="14">
+        <v>32</v>
+      </c>
+      <c r="D25" s="14">
+        <v>59</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-45.762711864406</v>
+      </c>
+      <c r="F25" s="14">
+        <v>105</v>
+      </c>
+      <c r="G25" s="14">
+        <v>176</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-40.340909090909</v>
+      </c>
+      <c r="I25" s="14">
+        <v>308</v>
+      </c>
+      <c r="J25" s="14">
+        <v>419</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-26.491646778043</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-32.307692307692</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>22</v>
-      </c>
-      <c r="D26" s="15">
-        <v>23</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-4.347826086956</v>
-      </c>
-      <c r="F26" s="15">
-        <v>67</v>
-      </c>
-      <c r="G26" s="15">
-        <v>75</v>
-      </c>
-      <c r="H26" s="14">
-        <v>-10.666666666666</v>
-      </c>
-      <c r="I26" s="15">
-        <v>177</v>
-      </c>
-      <c r="J26" s="15">
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>14</v>
+      </c>
+      <c r="E26" s="15">
+        <v>42.857142857142</v>
+      </c>
+      <c r="F26" s="14">
+        <v>76</v>
+      </c>
+      <c r="G26" s="14">
+        <v>71</v>
+      </c>
+      <c r="H26" s="15">
+        <v>7.042253521126</v>
+      </c>
+      <c r="I26" s="14">
         <v>196</v>
       </c>
-      <c r="K26" s="14">
-        <v>-9.693877551020</v>
-      </c>
-      <c r="L26" s="14">
-        <v>3.508771929824</v>
-      </c>
-      <c r="M26" s="14">
-        <v>36.153846153846</v>
+      <c r="J26" s="14">
+        <v>210</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-6.666666666666</v>
+      </c>
+      <c r="L26" s="15">
+        <v>4.255319148936</v>
+      </c>
+      <c r="M26" s="15">
+        <v>36.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
-        <v>4</v>
-      </c>
-      <c r="G27" s="15">
-        <v>3</v>
-      </c>
-      <c r="H27" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="I27" s="15">
-        <v>14</v>
-      </c>
-      <c r="J27" s="15">
-        <v>9</v>
-      </c>
-      <c r="K27" s="14">
-        <v>55.555555555555</v>
-      </c>
-      <c r="L27" s="14">
-        <v>100</v>
+      <c r="E27" s="15">
+        <v>200</v>
+      </c>
+      <c r="F27" s="14">
+        <v>6</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>200</v>
+      </c>
+      <c r="I27" s="14">
+        <v>17</v>
+      </c>
+      <c r="J27" s="14">
+        <v>10</v>
+      </c>
+      <c r="K27" s="15">
+        <v>70</v>
+      </c>
+      <c r="L27" s="15">
+        <v>142.857142857143</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>50</v>
-      </c>
-      <c r="F28" s="15">
-        <v>5</v>
-      </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
-      <c r="H28" s="14">
-        <v>25</v>
-      </c>
-      <c r="I28" s="15">
-        <v>13</v>
-      </c>
-      <c r="J28" s="15">
-        <v>21</v>
-      </c>
-      <c r="K28" s="14">
-        <v>-38.095238095238</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-53.571428571428</v>
+      <c r="H28" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="I28" s="14">
+        <v>17</v>
+      </c>
+      <c r="J28" s="14">
+        <v>21</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-19.047619047619</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-39.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1487,10 +1487,10 @@
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <v>1</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="15">
         <v>-100</v>
       </c>
       <c r="L29" s="13" t="s">
@@ -1499,7 +1499,7 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1528,10 +1528,10 @@
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="14">
         <v>1</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="15">
         <v>-100</v>
       </c>
       <c r="L30" s="13" t="s">
@@ -1540,7 +1540,7 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="15">
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>100</v>
+      </c>
+      <c r="I31" s="14">
         <v>5</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="14">
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
         <v>400</v>
+      </c>
+      <c r="L31" s="15">
+        <v>150</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,22 +1619,22 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="14">
         <v>1</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="15">
         <v>-100</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="15">
         <v>0</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="15">
         <v>-85.714285714285</v>
       </c>
       <c r="M33" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>19</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>11</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>3</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>5</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>3</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-40</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>0</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-72.727272727272</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-84.210526315789</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>33</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>34</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>28</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>22</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>43</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>95.454545454545</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>53.571428571428</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>26.470588235294</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>30.303030303030</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1220</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1217</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>480</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>388</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>252</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-35.051546391752</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-47.5</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-79.293344289235</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-79.344262295082</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>378</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>350</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>363</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>327</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>390</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>19.266055045871</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>7.438016528925</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>11.428571428571</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>3.174603174603</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>3189</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>2378</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>1440</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>964</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>448</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-53.526970954356</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-68.888888888888</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-81.160639192598</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-85.951708999686</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1877</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>1367</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>993</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>1175</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>1040</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-11.489361702127</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>4.733131923464</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-23.920994879297</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-44.592434736281</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>4813</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>4153</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>1668</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>1075</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>583</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-45.767441860465</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-65.047961630695</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-85.961955213099</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-87.886972782048</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -885,30 +885,30 @@
         <v>300</v>
       </c>
       <c r="N14" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>200</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
         <v>14</v>
@@ -926,7 +926,7 @@
         <v>366.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-83.333333333333</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-26.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.254901960784</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-62.352941176470</v>
+        <v>-63.043478260869</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.818181818181</v>
+        <v>-42.372881355932</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.321167883211</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>64</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I17" s="14">
+        <v>113</v>
+      </c>
+      <c r="J17" s="14">
         <v>105</v>
       </c>
-      <c r="J17" s="14">
-        <v>100</v>
-      </c>
       <c r="K17" s="15">
-        <v>5</v>
+        <v>7.619047619047</v>
       </c>
       <c r="L17" s="15">
-        <v>16.666666666666</v>
+        <v>10.784313725490</v>
       </c>
       <c r="M17" s="15">
-        <v>176.315789473684</v>
+        <v>156.818181818182</v>
       </c>
       <c r="N17" s="15">
-        <v>45.833333333333</v>
+        <v>39.506172839506</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H18" s="15">
-        <v>-43.589743589743</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I18" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J18" s="14">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K18" s="15">
-        <v>-48.031496062992</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="L18" s="15">
-        <v>-35.922330097087</v>
+        <v>-33.962264150943</v>
       </c>
       <c r="M18" s="15">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.926174496644</v>
+        <v>-89.079563182527</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>-38.461538461538</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.779220779220</v>
+        <v>-18.987341772151</v>
       </c>
       <c r="I19" s="14">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="J19" s="14">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.240740740740</v>
+        <v>-5.485232067510</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.666666666666</v>
+        <v>-36.543909348441</v>
       </c>
       <c r="M19" s="15">
-        <v>57.142857142857</v>
+        <v>48.344370860927</v>
       </c>
       <c r="N19" s="15">
-        <v>-25.886524822695</v>
+        <v>-27.272727272727</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
         <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20" s="14">
         <v>59</v>
       </c>
       <c r="G20" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>110.714285714286</v>
+        <v>90.322580645161</v>
       </c>
       <c r="I20" s="14">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J20" s="14">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K20" s="15">
-        <v>23.529411764705</v>
+        <v>23.214285714285</v>
       </c>
       <c r="L20" s="15">
-        <v>11.504424778761</v>
+        <v>8.661417322834</v>
       </c>
       <c r="M20" s="15">
-        <v>72.602739726027</v>
+        <v>81.578947368421</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.915887850467</v>
+        <v>-86.614936954413</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.644067796610</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="F21" s="17">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G21" s="17">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H21" s="18">
-        <v>9.677419354838</v>
+        <v>3.092783505154</v>
       </c>
       <c r="I21" s="17">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="J21" s="17">
-        <v>605</v>
+        <v>658</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.099173553719</v>
+        <v>-9.270516717325</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.415977961432</v>
+        <v>-23.949044585987</v>
       </c>
       <c r="M21" s="18">
-        <v>34.624697336561</v>
+        <v>31.497797356828</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.669703872437</v>
+        <v>-74.703389830508</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,13 +1201,13 @@
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
+        <v>-80</v>
+      </c>
+      <c r="L22" s="15">
         <v>-71.428571428571</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E24" s="15">
-        <v>-29.411764705882</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="G24" s="14">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.803418803418</v>
+        <v>-17.916666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>544</v>
+        <v>579</v>
       </c>
       <c r="J24" s="14">
-        <v>634</v>
+        <v>690</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.195583596214</v>
+        <v>-16.086956521739</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.617354196301</v>
+        <v>-22.593582887700</v>
       </c>
       <c r="M24" s="15">
-        <v>57.681159420289</v>
+        <v>59.504132231405</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.762711864406</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F25" s="14">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G25" s="14">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.340909090909</v>
+        <v>-41.242937853107</v>
       </c>
       <c r="I25" s="14">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="J25" s="14">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.491646778043</v>
+        <v>-30.885529157667</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.307692307692</v>
+        <v>-33.884297520661</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>42.857142857142</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G26" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H26" s="15">
-        <v>7.042253521126</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="I26" s="14">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="J26" s="14">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.666666666666</v>
+        <v>-9.130434782608</v>
       </c>
       <c r="L26" s="15">
-        <v>4.255319148936</v>
+        <v>0.480769230769</v>
       </c>
       <c r="M26" s="15">
-        <v>36.111111111111</v>
+        <v>37.5</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>200</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
         <v>17</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>7</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>133.333333333333</v>
+        <v>125</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-19.047619047619</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L28" s="15">
-        <v>-39.285714285714</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
         <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L31" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="I15" s="14">
+        <v>15</v>
+      </c>
+      <c r="J15" s="14">
+        <v>10</v>
+      </c>
+      <c r="K15" s="15">
+        <v>50</v>
+      </c>
+      <c r="L15" s="15">
         <v>150</v>
       </c>
-      <c r="I15" s="14">
-        <v>14</v>
-      </c>
-      <c r="J15" s="14">
-        <v>9</v>
-      </c>
-      <c r="K15" s="15">
-        <v>55.555555555555</v>
-      </c>
-      <c r="L15" s="15">
-        <v>250</v>
-      </c>
       <c r="M15" s="15">
-        <v>366.666666666667</v>
+        <v>275</v>
       </c>
       <c r="N15" s="15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-77.777777777777</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
         <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-43.333333333333</v>
+        <v>-43.75</v>
       </c>
       <c r="L16" s="15">
-        <v>-63.043478260869</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.372881355932</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.235294117647</v>
+        <v>-88.196721311475</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
         <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>44.444444444444</v>
+        <v>79.166666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>7.619047619047</v>
+        <v>20</v>
       </c>
       <c r="L17" s="15">
-        <v>10.784313725490</v>
+        <v>16.814159292035</v>
       </c>
       <c r="M17" s="15">
-        <v>156.818181818182</v>
+        <v>153.846153846154</v>
       </c>
       <c r="N17" s="15">
-        <v>39.506172839506</v>
+        <v>46.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H18" s="15">
-        <v>-45.454545454545</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I18" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J18" s="14">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="K18" s="15">
-        <v>-48.148148148148</v>
+        <v>-51.006711409396</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.962264150943</v>
+        <v>-34.821428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-41.666666666666</v>
+        <v>-43.410852713178</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.079563182527</v>
+        <v>-89.296187683284</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="F19" s="14">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.987341772151</v>
+        <v>-19.480519480519</v>
       </c>
       <c r="I19" s="14">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="J19" s="14">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.485232067510</v>
+        <v>-8.203125</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.543909348441</v>
+        <v>-36.486486486486</v>
       </c>
       <c r="M19" s="15">
-        <v>48.344370860927</v>
+        <v>41.566265060241</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.272727272727</v>
+        <v>-29.003021148036</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
         <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G20" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H20" s="15">
-        <v>90.322580645161</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J20" s="14">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="K20" s="15">
-        <v>23.214285714285</v>
+        <v>22.131147540983</v>
       </c>
       <c r="L20" s="15">
-        <v>8.661417322834</v>
+        <v>9.558823529411</v>
       </c>
       <c r="M20" s="15">
-        <v>81.578947368421</v>
+        <v>83.950617283950</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.614936954413</v>
+        <v>-86.405109489051</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
         <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.415094339622</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="F21" s="17">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G21" s="17">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H21" s="18">
-        <v>3.092783505154</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="I21" s="17">
-        <v>597</v>
+        <v>644</v>
       </c>
       <c r="J21" s="17">
-        <v>658</v>
+        <v>711</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.270516717325</v>
+        <v>-9.423347398030</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.949044585987</v>
+        <v>-23.058542413381</v>
       </c>
       <c r="M21" s="18">
-        <v>31.497797356828</v>
+        <v>29.838709677419</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.703389830508</v>
+        <v>-74.383452665075</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-80</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="L22" s="15">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>21</v>
+        <v>-57.142857142857</v>
+      </c>
+      <c r="M22" s="15">
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14">
         <v>2</v>
       </c>
-      <c r="G23" s="14">
-        <v>3</v>
-      </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J23" s="14">
         <v>5</v>
       </c>
       <c r="K23" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L23" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.5</v>
+        <v>-14</v>
       </c>
       <c r="F24" s="14">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G24" s="14">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="H24" s="15">
-        <v>-17.916666666666</v>
+        <v>-16.228070175438</v>
       </c>
       <c r="I24" s="14">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="J24" s="14">
-        <v>690</v>
+        <v>740</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.086956521739</v>
+        <v>-15.945945945945</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.593582887700</v>
+        <v>-21.563682219419</v>
       </c>
       <c r="M24" s="15">
-        <v>59.504132231405</v>
+        <v>57.868020304568</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15">
-        <v>-72.727272727272</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="F25" s="14">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G25" s="14">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H25" s="15">
-        <v>-41.242937853107</v>
+        <v>-39.880952380952</v>
       </c>
       <c r="I25" s="14">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="J25" s="14">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.885529157667</v>
+        <v>-31.781376518218</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.884297520661</v>
+        <v>-34.563106796116</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>-30</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="F26" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.194805194805</v>
+        <v>-1.265822784810</v>
       </c>
       <c r="I26" s="14">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="J26" s="14">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.130434782608</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L26" s="15">
-        <v>0.480769230769</v>
+        <v>1.785714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>37.5</v>
+        <v>34.117647058823</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>70</v>
+        <v>72.727272727272</v>
       </c>
       <c r="L27" s="15">
-        <v>142.857142857143</v>
+        <v>111.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.636363636363</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L28" s="15">
-        <v>-34.482758620689</v>
+        <v>-37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,14 +1484,14 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,15 +1500,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,14 +1525,14 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>4</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>63.636363636363</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="N15" s="15">
-        <v>87.5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>75</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>-63.636363636363</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K16" s="15">
-        <v>-43.75</v>
+        <v>-36.764705882352</v>
       </c>
       <c r="L16" s="15">
-        <v>-63.636363636363</v>
+        <v>-60.909090909090</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.857142857142</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.196721311475</v>
+        <v>-86.850152905198</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>240</v>
+        <v>62.5</v>
       </c>
       <c r="F17" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>79.166666666666</v>
+        <v>100</v>
       </c>
       <c r="I17" s="14">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="J17" s="14">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K17" s="15">
-        <v>20</v>
+        <v>23.728813559322</v>
       </c>
       <c r="L17" s="15">
-        <v>16.814159292035</v>
+        <v>21.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>153.846153846154</v>
+        <v>165.454545454545</v>
       </c>
       <c r="N17" s="15">
-        <v>46.666666666666</v>
+        <v>53.684210526315</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-85.714285714285</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H18" s="15">
-        <v>-61.904761904761</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J18" s="14">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.006711409396</v>
+        <v>-49.677419354838</v>
       </c>
       <c r="L18" s="15">
-        <v>-34.821428571428</v>
+        <v>-35</v>
       </c>
       <c r="M18" s="15">
-        <v>-43.410852713178</v>
+        <v>-43.884892086330</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.296187683284</v>
+        <v>-89.430894308943</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-52.631578947368</v>
+        <v>5.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.480519480519</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="J19" s="14">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.203125</v>
+        <v>-7.299270072992</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.486486486486</v>
+        <v>-36.972704714640</v>
       </c>
       <c r="M19" s="15">
-        <v>41.566265060241</v>
+        <v>46.820809248554</v>
       </c>
       <c r="N19" s="15">
-        <v>-29.003021148036</v>
+        <v>-29.247910863509</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G20" s="14">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H20" s="15">
-        <v>54.545454545454</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="I20" s="14">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="J20" s="14">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K20" s="15">
-        <v>22.131147540983</v>
+        <v>16.058394160583</v>
       </c>
       <c r="L20" s="15">
-        <v>9.558823529411</v>
+        <v>8.904109589041</v>
       </c>
       <c r="M20" s="15">
-        <v>83.950617283950</v>
+        <v>89.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.405109489051</v>
+        <v>-86.570945945946</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.641509433962</v>
+        <v>9.615384615384</v>
       </c>
       <c r="F21" s="17">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G21" s="17">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.970149253731</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>644</v>
+        <v>702</v>
       </c>
       <c r="J21" s="17">
-        <v>711</v>
+        <v>763</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.423347398030</v>
+        <v>-7.994757536041</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.058542413381</v>
+        <v>-22.516556291390</v>
       </c>
       <c r="M21" s="18">
-        <v>29.838709677419</v>
+        <v>34.225621414914</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.383452665075</v>
+        <v>-74.124585329893</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
+      <c r="E22" s="15">
+        <v>100</v>
+      </c>
+      <c r="F22" s="14">
         <v>3</v>
       </c>
-      <c r="E22" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>-85.714285714285</v>
+        <v>-62.5</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-76.923076923076</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>-57.142857142857</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>10</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D24" s="14">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-14</v>
+        <v>21.621621621621</v>
       </c>
       <c r="F24" s="14">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="G24" s="14">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.228070175438</v>
+        <v>-18.483412322274</v>
       </c>
       <c r="I24" s="14">
-        <v>622</v>
+        <v>667</v>
       </c>
       <c r="J24" s="14">
-        <v>740</v>
+        <v>777</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.945945945945</v>
+        <v>-14.157014157014</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.563682219419</v>
+        <v>-21.158392434988</v>
       </c>
       <c r="M24" s="15">
-        <v>57.868020304568</v>
+        <v>59.952038369304</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.161290322580</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F25" s="14">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="G25" s="14">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.880952380952</v>
+        <v>-50.322580645161</v>
       </c>
       <c r="I25" s="14">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="J25" s="14">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.781376518218</v>
+        <v>-31.456310679611</v>
       </c>
       <c r="L25" s="15">
-        <v>-34.563106796116</v>
+        <v>-36.510791366906</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-4.545454545454</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F26" s="14">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G26" s="14">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.265822784810</v>
+        <v>-2.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="J26" s="14">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.523809523809</v>
+        <v>-9.594095940959</v>
       </c>
       <c r="L26" s="15">
-        <v>1.785714285714</v>
+        <v>1.659751037344</v>
       </c>
       <c r="M26" s="15">
-        <v>34.117647058823</v>
+        <v>25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>72.727272727272</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>111.111111111111</v>
+        <v>144.444444444444</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.043478260869</v>
+        <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-37.5</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>200</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>18</v>
@@ -920,7 +920,7 @@
         <v>63.636363636363</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>157.142857142857</v>
       </c>
       <c r="M15" s="15">
         <v>350</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-47.826086956521</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J16" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K16" s="15">
-        <v>-36.764705882352</v>
+        <v>-35.211267605633</v>
       </c>
       <c r="L16" s="15">
-        <v>-60.909090909090</v>
+        <v>-61.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.820895522388</v>
+        <v>-31.343283582089</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.850152905198</v>
+        <v>-86.819484240687</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>62.5</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F17" s="14">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>100</v>
+        <v>41.379310344827</v>
       </c>
       <c r="I17" s="14">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J17" s="14">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="K17" s="15">
-        <v>23.728813559322</v>
+        <v>15.503875968992</v>
       </c>
       <c r="L17" s="15">
-        <v>21.666666666666</v>
+        <v>15.503875968992</v>
       </c>
       <c r="M17" s="15">
-        <v>165.454545454545</v>
+        <v>144.262295081967</v>
       </c>
       <c r="N17" s="15">
-        <v>53.684210526315</v>
+        <v>46.078431372549</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-16.666666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
         <v>36</v>
       </c>
       <c r="H18" s="15">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J18" s="14">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.677419354838</v>
+        <v>-47.852760736196</v>
       </c>
       <c r="L18" s="15">
-        <v>-35</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M18" s="15">
-        <v>-43.884892086330</v>
+        <v>-41.780821917808</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.430894308943</v>
+        <v>-89.199491740787</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
         <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>5.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H19" s="15">
-        <v>-32.142857142857</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I19" s="14">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="J19" s="14">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.299270072992</v>
+        <v>-9.589041095890</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.972704714640</v>
+        <v>-39.030023094688</v>
       </c>
       <c r="M19" s="15">
-        <v>46.820809248554</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N19" s="15">
-        <v>-29.247910863509</v>
+        <v>-32.307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H20" s="15">
-        <v>-4.444444444444</v>
+        <v>-16</v>
       </c>
       <c r="I20" s="14">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J20" s="14">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K20" s="15">
-        <v>16.058394160583</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L20" s="15">
-        <v>8.904109589041</v>
+        <v>5.660377358490</v>
       </c>
       <c r="M20" s="15">
-        <v>89.285714285714</v>
+        <v>84.615384615384</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.570945945946</v>
+        <v>-86.687797147385</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>9.615384615384</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="17">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="G21" s="17">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.285714285714</v>
+        <v>-19.718309859154</v>
       </c>
       <c r="I21" s="17">
-        <v>702</v>
+        <v>734</v>
       </c>
       <c r="J21" s="17">
-        <v>763</v>
+        <v>818</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.994757536041</v>
+        <v>-10.268948655256</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.516556291390</v>
+        <v>-25.025536261491</v>
       </c>
       <c r="M21" s="18">
-        <v>34.225621414914</v>
+        <v>31.777378815080</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.124585329893</v>
+        <v>-74.689655172413</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>-62.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-64.285714285714</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L22" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M22" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
@@ -1242,13 +1242,13 @@
         <v>10</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M23" s="15">
         <v>233.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>21.621621621621</v>
+        <v>61.764705882352</v>
       </c>
       <c r="F24" s="14">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G24" s="14">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.483412322274</v>
+        <v>1.129943502824</v>
       </c>
       <c r="I24" s="14">
-        <v>667</v>
+        <v>722</v>
       </c>
       <c r="J24" s="14">
-        <v>777</v>
+        <v>811</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.157014157014</v>
+        <v>-10.974106041923</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.158392434988</v>
+        <v>-19.688542825361</v>
       </c>
       <c r="M24" s="15">
-        <v>59.952038369304</v>
+        <v>61.883408071748</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.809523809523</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F25" s="14">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" s="14">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="H25" s="15">
-        <v>-50.322580645161</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="I25" s="14">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="J25" s="14">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.456310679611</v>
+        <v>-28.119180633147</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.510791366906</v>
+        <v>-34.907251264755</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.263157894736</v>
+        <v>-31.25</v>
       </c>
       <c r="F26" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G26" s="14">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.666666666666</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I26" s="14">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="J26" s="14">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.594095940959</v>
+        <v>-11.881188118811</v>
       </c>
       <c r="L26" s="15">
-        <v>1.659751037344</v>
+        <v>3.488372093023</v>
       </c>
       <c r="M26" s="15">
-        <v>25</v>
+        <v>23.611111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>200</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
         <v>22</v>
@@ -1412,7 +1412,7 @@
         <v>83.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>144.444444444444</v>
+        <v>120</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>166.666666666667</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K28" s="15">
-        <v>-12.5</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L28" s="15">
-        <v>-40</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="14">
+        <v>6</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>300</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -879,7 +879,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M14" s="15">
         <v>300</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="14">
         <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>63.636363636363</v>
+        <v>72.727272727272</v>
       </c>
       <c r="L15" s="15">
-        <v>157.142857142857</v>
+        <v>171.428571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="N15" s="15">
-        <v>125</v>
+        <v>111.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>-30</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.211267605633</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="L16" s="15">
-        <v>-61.666666666666</v>
+        <v>-59.523809523809</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.343283582089</v>
+        <v>-27.142857142857</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.819484240687</v>
+        <v>-86.71875</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-72.727272727272</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>41.379310344827</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I17" s="14">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="J17" s="14">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="K17" s="15">
-        <v>15.503875968992</v>
+        <v>13.888888888888</v>
       </c>
       <c r="L17" s="15">
-        <v>15.503875968992</v>
+        <v>21.481481481481</v>
       </c>
       <c r="M17" s="15">
-        <v>144.262295081967</v>
+        <v>160.31746031746</v>
       </c>
       <c r="N17" s="15">
-        <v>46.078431372549</v>
+        <v>49.090909090909</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>6</v>
+      </c>
+      <c r="D18" s="14">
         <v>7</v>
       </c>
-      <c r="D18" s="14">
-        <v>8</v>
-      </c>
       <c r="E18" s="15">
-        <v>-12.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J18" s="14">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.852760736196</v>
+        <v>-45.882352941176</v>
       </c>
       <c r="L18" s="15">
-        <v>-34.615384615384</v>
+        <v>-33.812949640287</v>
       </c>
       <c r="M18" s="15">
-        <v>-41.780821917808</v>
+        <v>-41.772151898734</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.199491740787</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>6.25</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.578947368421</v>
+        <v>-22.535211267605</v>
       </c>
       <c r="I19" s="14">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="J19" s="14">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.589041095890</v>
+        <v>-8.766233766233</v>
       </c>
       <c r="L19" s="15">
-        <v>-39.030023094688</v>
+        <v>-39.699570815450</v>
       </c>
       <c r="M19" s="15">
-        <v>41.176470588235</v>
+        <v>41.206030150753</v>
       </c>
       <c r="N19" s="15">
-        <v>-32.307692307692</v>
+        <v>-33.412322274881</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="F20" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G20" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H20" s="15">
-        <v>-16</v>
+        <v>-38.983050847457</v>
       </c>
       <c r="I20" s="14">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J20" s="14">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K20" s="15">
-        <v>10.526315789473</v>
+        <v>2.339181286549</v>
       </c>
       <c r="L20" s="15">
-        <v>5.660377358490</v>
+        <v>4.790419161676</v>
       </c>
       <c r="M20" s="15">
-        <v>84.615384615384</v>
+        <v>84.210526315789</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.687797147385</v>
+        <v>-86.861861861861</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>-21.875</v>
       </c>
       <c r="F21" s="17">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G21" s="17">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.718309859154</v>
+        <v>-19.196428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>734</v>
+        <v>786</v>
       </c>
       <c r="J21" s="17">
-        <v>818</v>
+        <v>882</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.268948655256</v>
+        <v>-10.884353741496</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.025536261491</v>
+        <v>-24.568138195777</v>
       </c>
       <c r="M21" s="18">
-        <v>31.777378815080</v>
+        <v>33.220338983050</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.689655172413</v>
+        <v>-74.538386783284</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-42.857142857142</v>
+        <v>-20</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="L22" s="15">
         <v>-14.285714285714</v>
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="E24" s="15">
-        <v>61.764705882352</v>
+        <v>-39.436619718309</v>
       </c>
       <c r="F24" s="14">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G24" s="14">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="H24" s="15">
-        <v>1.129943502824</v>
+        <v>-3.125</v>
       </c>
       <c r="I24" s="14">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="J24" s="14">
-        <v>811</v>
+        <v>882</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.974106041923</v>
+        <v>-13.378684807256</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.688542825361</v>
+        <v>-19.324181626188</v>
       </c>
       <c r="M24" s="15">
-        <v>61.883408071748</v>
+        <v>59.166666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E25" s="15">
-        <v>45.454545454545</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G25" s="14">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="H25" s="15">
-        <v>-33.898305084745</v>
+        <v>-25.688073394495</v>
       </c>
       <c r="I25" s="14">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="J25" s="14">
-        <v>537</v>
+        <v>572</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.119180633147</v>
+        <v>-29.895104895104</v>
       </c>
       <c r="L25" s="15">
-        <v>-34.907251264755</v>
+        <v>-35.737179487179</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-31.25</v>
+        <v>69.230769230769</v>
       </c>
       <c r="F26" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G26" s="14">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.354838709677</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="I26" s="14">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="J26" s="14">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.881188118811</v>
+        <v>-9.177215189873</v>
       </c>
       <c r="L26" s="15">
-        <v>3.488372093023</v>
+        <v>3.237410071942</v>
       </c>
       <c r="M26" s="15">
-        <v>23.611111111111</v>
+        <v>26.431718061674</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>83.333333333333</v>
+        <v>108.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>4</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.518518518518</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-38.888888888888</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
@@ -1561,22 +1561,22 @@
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K31" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="L31" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-109pct.xlsx
+++ b/data/source/weekly/cs-en-us-109pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>7</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>5</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="I15" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J15" s="14">
         <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>72.727272727272</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>171.428571428571</v>
+        <v>175</v>
       </c>
       <c r="M15" s="15">
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="N15" s="15">
-        <v>111.111111111111</v>
+        <v>144.444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
         <v>5</v>
       </c>
-      <c r="D16" s="14">
-        <v>7</v>
-      </c>
       <c r="E16" s="15">
-        <v>-28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>-5.555555555555</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I16" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.615384615384</v>
+        <v>-34.939759036144</v>
       </c>
       <c r="L16" s="15">
-        <v>-59.523809523809</v>
+        <v>-59.398496240601</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.142857142857</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.71875</v>
+        <v>-87.173396674584</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-13.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H17" s="15">
-        <v>23.076923076923</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I17" s="14">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J17" s="14">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K17" s="15">
-        <v>13.888888888888</v>
+        <v>11.688311688311</v>
       </c>
       <c r="L17" s="15">
-        <v>21.481481481481</v>
+        <v>15.436241610738</v>
       </c>
       <c r="M17" s="15">
-        <v>160.31746031746</v>
+        <v>164.615384615385</v>
       </c>
       <c r="N17" s="15">
-        <v>49.090909090909</v>
+        <v>45.762711864406</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-14.285714285714</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G18" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="I18" s="14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J18" s="14">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.882352941176</v>
+        <v>-45.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.812949640287</v>
+        <v>-32.876712328767</v>
       </c>
       <c r="M18" s="15">
-        <v>-41.772151898734</v>
+        <v>-41.317365269461</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.888888888888</v>
+        <v>-88.722669735328</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>6.25</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G19" s="14">
         <v>71</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.535211267605</v>
+        <v>-15.492957746478</v>
       </c>
       <c r="I19" s="14">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="J19" s="14">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.766233766233</v>
+        <v>-8.868501529051</v>
       </c>
       <c r="L19" s="15">
-        <v>-39.699570815450</v>
+        <v>-40.160642570281</v>
       </c>
       <c r="M19" s="15">
-        <v>41.206030150753</v>
+        <v>35.454545454545</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.412322274881</v>
+        <v>-35.637149028077</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D20" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.894736842105</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G20" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H20" s="15">
-        <v>-38.983050847457</v>
+        <v>-32.786885245901</v>
       </c>
       <c r="I20" s="14">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="J20" s="14">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="K20" s="15">
-        <v>2.339181286549</v>
+        <v>3.278688524590</v>
       </c>
       <c r="L20" s="15">
-        <v>4.790419161676</v>
+        <v>6.179775280898</v>
       </c>
       <c r="M20" s="15">
-        <v>84.210526315789</v>
+        <v>90.909090909090</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.861861861861</v>
+        <v>-86.576704545454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.875</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G21" s="17">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.196428571428</v>
+        <v>-17.180616740088</v>
       </c>
       <c r="I21" s="17">
-        <v>786</v>
+        <v>837</v>
       </c>
       <c r="J21" s="17">
-        <v>882</v>
+        <v>938</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.884353741496</v>
+        <v>-10.767590618336</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.568138195777</v>
+        <v>-24.865350089766</v>
       </c>
       <c r="M21" s="18">
-        <v>33.220338983050</v>
+        <v>33.280254777070</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.538386783284</v>
+        <v>-74.559270516717</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
         <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>-60</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1229,14 +1229,14 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>10</v>
@@ -1248,7 +1248,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="M23" s="15">
         <v>233.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D24" s="14">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E24" s="15">
-        <v>-39.436619718309</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="F24" s="14">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G24" s="14">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.125</v>
+        <v>-8.5</v>
       </c>
       <c r="I24" s="14">
-        <v>764</v>
+        <v>803</v>
       </c>
       <c r="J24" s="14">
-        <v>882</v>
+        <v>940</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.378684807256</v>
+        <v>-14.574468085106</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.324181626188</v>
+        <v>-19.296482412060</v>
       </c>
       <c r="M24" s="15">
-        <v>59.166666666666</v>
+        <v>55.620155038759</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D25" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" s="15">
-        <v>-57.142857142857</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G25" s="14">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H25" s="15">
-        <v>-25.688073394495</v>
+        <v>-22.807017543859</v>
       </c>
       <c r="I25" s="14">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="J25" s="14">
-        <v>572</v>
+        <v>608</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.895104895104</v>
+        <v>-30.098684210526</v>
       </c>
       <c r="L25" s="15">
-        <v>-35.737179487179</v>
+        <v>-33.903576982892</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>69.230769230769</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F26" s="14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.813953488372</v>
+        <v>4</v>
       </c>
       <c r="I26" s="14">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="J26" s="14">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.177215189873</v>
+        <v>-7.033639143730</v>
       </c>
       <c r="L26" s="15">
-        <v>3.237410071942</v>
+        <v>3.050847457627</v>
       </c>
       <c r="M26" s="15">
-        <v>26.431718061674</v>
+        <v>26.141078838174</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="I27" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>108.333333333333</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>150</v>
+        <v>154.545454545455</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>16.666666666666</v>
+        <v>60</v>
       </c>
       <c r="I28" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
         <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-29.729729729729</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>-37.5</v>
       </c>
       <c r="L31" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-85.714285714285</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
